--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.24201102061498</v>
+        <v>13.20182679084994</v>
       </c>
       <c r="D2" t="n">
-        <v>82.5045822725582</v>
+        <v>13.40699461929071</v>
       </c>
       <c r="E2" t="n">
-        <v>9.299273241976117</v>
+        <v>1.511131901821119</v>
       </c>
       <c r="F2" t="n">
-        <v>9.862526505981632</v>
+        <v>1.602660557222015</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.89530788344467</v>
+        <v>9.895487531059759</v>
       </c>
       <c r="D3" t="n">
-        <v>61.12746897291195</v>
+        <v>9.933213708098192</v>
       </c>
       <c r="E3" t="n">
-        <v>9.299273241976117</v>
+        <v>1.511131901821119</v>
       </c>
       <c r="F3" t="n">
-        <v>9.862526505981632</v>
+        <v>1.602660557222015</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.9362568147106</v>
+        <v>8.764641732390473</v>
       </c>
       <c r="D4" t="n">
-        <v>53.67891547142248</v>
+        <v>8.722823764106153</v>
       </c>
       <c r="E4" t="n">
-        <v>9.299273241976117</v>
+        <v>1.511131901821119</v>
       </c>
       <c r="F4" t="n">
-        <v>9.862526505981632</v>
+        <v>1.602660557222015</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.52048388424359</v>
+        <v>10.97207863118958</v>
       </c>
       <c r="D5" t="n">
-        <v>66.39073308392655</v>
+        <v>10.78849412613807</v>
       </c>
       <c r="E5" t="n">
-        <v>9.299273241976117</v>
+        <v>1.511131901821119</v>
       </c>
       <c r="F5" t="n">
-        <v>9.862526505981632</v>
+        <v>1.602660557222015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.17563771725675</v>
+        <v>9.778541129054222</v>
       </c>
       <c r="D6" t="n">
-        <v>59.00942897589331</v>
+        <v>9.589032208582664</v>
       </c>
       <c r="E6" t="n">
-        <v>9.299273241976117</v>
+        <v>1.511131901821119</v>
       </c>
       <c r="F6" t="n">
-        <v>9.862526505981632</v>
+        <v>1.602660557222015</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
